--- a/data/trans_orig/P16A_2_R3-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_2_R3-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154658</t>
+          <t>155822</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>194177</t>
+          <t>194543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>431010</t>
+          <t>425820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>472272</t>
+          <t>470787</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>594469</t>
+          <t>594487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>653229</t>
+          <t>654772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>320761</t>
+          <t>320395</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>360280</t>
+          <t>359116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283236</t>
+          <t>284721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>324498</t>
+          <t>329688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>617217</t>
+          <t>615674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>675977</t>
+          <t>675959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>319813</t>
+          <t>329392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>538135</t>
+          <t>537788</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>721549</t>
+          <t>718916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1277938</t>
+          <t>1194780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1140902</t>
+          <t>1103784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1828461</t>
+          <t>1812418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1752192</t>
+          <t>1752539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1970514</t>
+          <t>1960935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>959885</t>
+          <t>1043043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1516274</t>
+          <t>1518907</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2699689</t>
+          <t>2715732</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3387248</t>
+          <t>3424366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104500</t>
+          <t>105392</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149159</t>
+          <t>150066</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170539</t>
+          <t>172697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>212639</t>
+          <t>213359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289619</t>
+          <t>287562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>349884</t>
+          <t>349212</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497464</t>
+          <t>496557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542123</t>
+          <t>541231</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447824</t>
+          <t>447104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>489924</t>
+          <t>487766</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>957202</t>
+          <t>957874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1017467</t>
+          <t>1019524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>606901</t>
+          <t>595630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>847629</t>
+          <t>847207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1364622</t>
+          <t>1364056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1912429</t>
+          <t>1907600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2054571</t>
+          <t>2045475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2776051</t>
+          <t>2723080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2604260</t>
+          <t>2604682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2844988</t>
+          <t>2856259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1741365</t>
+          <t>1746194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2289172</t>
+          <t>2289738</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4329632</t>
+          <t>4382603</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5051112</t>
+          <t>5060208</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_2_R3-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_2_R3-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>173541</t>
+          <t>187090</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155822</t>
+          <t>166207</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>194543</t>
+          <t>209223</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>449881</t>
+          <t>484423</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>425820</t>
+          <t>463693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>470787</t>
+          <t>506797</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>623422</t>
+          <t>671513</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>594487</t>
+          <t>635907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>654772</t>
+          <t>700868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>341397</t>
+          <t>391439</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>320395</t>
+          <t>369306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>359116</t>
+          <t>412322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>305627</t>
+          <t>337615</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284721</t>
+          <t>315241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329688</t>
+          <t>358345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>647024</t>
+          <t>729054</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>615674</t>
+          <t>699699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>675959</t>
+          <t>764660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>467018</t>
+          <t>502140</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>329392</t>
+          <t>456577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>537788</t>
+          <t>549763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>876718</t>
+          <t>741359</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>718916</t>
+          <t>701824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1194780</t>
+          <t>781740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1343736</t>
+          <t>1243500</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1103784</t>
+          <t>1187413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1812418</t>
+          <t>1310611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1823309</t>
+          <t>1728426</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1752539</t>
+          <t>1680803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1960935</t>
+          <t>1773989</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1361105</t>
+          <t>1430033</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1043043</t>
+          <t>1389652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1518907</t>
+          <t>1469568</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3184414</t>
+          <t>3158459</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2715732</t>
+          <t>3091348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3424366</t>
+          <t>3214546</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>125156</t>
+          <t>137511</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105392</t>
+          <t>117136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150066</t>
+          <t>163727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>192288</t>
+          <t>210566</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172697</t>
+          <t>189519</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>213359</t>
+          <t>234889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>317444</t>
+          <t>348077</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287562</t>
+          <t>317274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>349212</t>
+          <t>378580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>521467</t>
+          <t>574076</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>496557</t>
+          <t>547860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541231</t>
+          <t>594451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>468175</t>
+          <t>524311</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447104</t>
+          <t>499988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>487766</t>
+          <t>545358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>989642</t>
+          <t>1098387</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>957874</t>
+          <t>1067884</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1019524</t>
+          <t>1129190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,07%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>765715</t>
+          <t>826742</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>595630</t>
+          <t>776710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>847207</t>
+          <t>881285</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1518887</t>
+          <t>1436347</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1364056</t>
+          <t>1385671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1907600</t>
+          <t>1489252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2284603</t>
+          <t>2263090</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2045475</t>
+          <t>2187628</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2723080</t>
+          <t>2333372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2686174</t>
+          <t>2693941</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2604682</t>
+          <t>2639398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2856259</t>
+          <t>2743973</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2134907</t>
+          <t>2291960</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1746194</t>
+          <t>2239055</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2289738</t>
+          <t>2342636</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4821080</t>
+          <t>4985900</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4382603</t>
+          <t>4915618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5060208</t>
+          <t>5061362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
